--- a/results/job_matches_2026-04-20.xlsx
+++ b/results/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,6 +532,41 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2020840dfc5b5027</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-20.xlsx
+++ b/results/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,68 +503,103 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer (React UI) - Remote US</t>
+          <t>Business Analyst Sr</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cielo</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wauwatosa, WI, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>AI Engineer (React UI) - Remote US</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cielo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Wauwatosa, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Houston, TX, US USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>10.4</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2020840dfc5b5027</t>
         </is>

--- a/results/job_matches_2026-04-20.xlsx
+++ b/results/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks / IAM</t>
+          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aaafa9ff6580061</t>
+          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
         </is>
       </c>
     </row>
@@ -538,68 +538,138 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer (React UI) - Remote US</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cielo</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wauwatosa, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, Airflow</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>State of Ohio</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AI Engineer (React UI) - Remote US</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cielo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Wauwatosa, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Houston, TX, US USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D7" t="n">
         <v>10.4</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2020840dfc5b5027</t>
         </is>

--- a/results/job_matches_2026-04-20.xlsx
+++ b/results/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Alkami Technology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.2</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9c766989d27507</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Business Analyst Sr</t>
+          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
+          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Business Analyst Sr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,75 +601,110 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer (React UI) - Remote US</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cielo</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wauwatosa, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>AI Engineer (React UI) - Remote US</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cielo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Wauwatosa, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Houston, TX, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>10.4</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2020840dfc5b5027</t>
         </is>

--- a/results/job_matches_2026-04-20.xlsx
+++ b/results/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
+          <t>Architect with AWS and Data Bricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
+          <t>AWS, Lambda, S3, RDS, Google Cloud Platform, Cloud Storage, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c581906df4e1c3dd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Business Analyst Sr</t>
+          <t>Compute - New</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>India Hook, SC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Business Analyst Sr</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,77 +636,112 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer (React UI) - Remote US</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cielo</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wauwatosa, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Engineer (React UI) - Remote US</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cielo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wauwatosa, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2020840dfc5b5027</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-20.xlsx
+++ b/results/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Architect with AWS and Data Bricks</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Google Cloud Platform, Cloud Storage, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c581906df4e1c3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
         </is>
       </c>
     </row>
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Data Engineer | Buy Side</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Mosaic Partners</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, Spark, Scala, Snowflake, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,217 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=1f51528459a436b7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer (React UI) - Remote US</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cielo</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wauwatosa, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI Engineer-Machine Learning Platform</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Global Servicing Technology</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>11.8</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NBCUniversal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-20.xlsx
+++ b/results/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compute - New</t>
+          <t>GCP Data Cloud Architect with AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Hook, SC, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
+          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
+          <t>AI Integration Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a7d79dfeae2865</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Business Analyst Sr</t>
+          <t>AI Integration Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
+          <t>https://www.indeed.com/viewjob?jk=c810855cd475cddf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Compute - New</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>India Hook, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer | Buy Side</t>
+          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mosaic Partners</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, Spark, Scala, Snowflake, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f51528459a436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Business Analyst Sr</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer-Machine Learning Platform</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,112 +766,112 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,742 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>State of Ohio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Engineer-Machine Learning Platform</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Global Servicing Technology</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CG Infinity</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af6f9746ce15f110</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CG Infinity</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92f7fca632ed3f48</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Unity Catalog, Cloud Storage, Spark, Scala, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>NBCUniversal</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D25" t="n">
         <v>10.4</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Menomonee Falls, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Galesburg, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Moon Township, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Southfield, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>API Architect</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e1e187ea4c6001c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-20.xlsx
+++ b/results/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alkami Technology</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9c766989d27507</t>
+          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>GCP Data Cloud Architect with AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
+          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GCP Data Cloud Architect with AI</t>
+          <t>AI Integration Consultant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a7d79dfeae2865</t>
         </is>
       </c>
     </row>
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a7d79dfeae2865</t>
+          <t>https://www.indeed.com/viewjob?jk=c810855cd475cddf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Integration Consultant</t>
+          <t>Compute - New</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>India Hook, SC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c810855cd475cddf</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Compute - New</t>
+          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India Hook, SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
+          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
+          <t>Business Analyst Sr</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Business Analyst Sr</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
+          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
+          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>AI Engineer-Machine Learning Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer-Machine Learning Platform</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=af6f9746ce15f110</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7fca632ed3f48</t>
         </is>
       </c>
     </row>
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af6f9746ce15f110</t>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7fca632ed3f48</t>
+          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
         </is>
       </c>
     </row>
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, S3, IAM, RDS, Unity Catalog, Cloud Storage, Spark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Unity Catalog, Cloud Storage, Spark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>API Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=9e1e187ea4c6001c</t>
         </is>
       </c>
     </row>
@@ -1582,41 +1582,6 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>API Architect</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1e187ea4c6001c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-20.xlsx
+++ b/results/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GCP Data Cloud Architect with AI</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
+          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Integration Consultant</t>
+          <t>GCP Data Cloud Architect with AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a7d79dfeae2865</t>
+          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
         </is>
       </c>
     </row>
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c810855cd475cddf</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a7d79dfeae2865</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Compute - New</t>
+          <t>AI Integration Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Hook, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
+          <t>https://www.indeed.com/viewjob?jk=c810855cd475cddf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
+          <t>Compute - New</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>India Hook, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
+          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Business Analyst Sr</t>
+          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
+          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Business Analyst Sr</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Site Reliability Engineer (Azure)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>IAM, RDS, Azure, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
+          <t>https://www.indeed.com/viewjob?jk=68867f5f2f53aa49</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer-Machine Learning Platform</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,139 +941,139 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
+          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>AI Engineer-Machine Learning Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af6f9746ce15f110</t>
+          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7fca632ed3f48</t>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
         </is>
       </c>
     </row>
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Unity Catalog, Cloud Storage, Spark, Scala, MLflow, CI/CD</t>
+          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
+          <t>https://www.indeed.com/viewjob?jk=af6f9746ce15f110</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7fca632ed3f48</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>API Architect</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Unity Catalog, Cloud Storage, Spark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1e187ea4c6001c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,112 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>University of Utah</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-20.xlsx
+++ b/results/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GCP Data Cloud Architect with AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
+          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Integration Consultant</t>
+          <t>GCP Data Cloud Architect with AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a7d79dfeae2865</t>
+          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
         </is>
       </c>
     </row>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c810855cd475cddf</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a7d79dfeae2865</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Compute - New</t>
+          <t>AI Integration Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>India Hook, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
+          <t>https://www.indeed.com/viewjob?jk=c810855cd475cddf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
+          <t>Compute - New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>India Hook, SC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
+          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Business Analyst Sr</t>
+          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
+          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Azure)</t>
+          <t>Business Analyst Sr</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,52 +766,52 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68867f5f2f53aa49</t>
+          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Site Reliability Engineer (Azure)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>IAM, RDS, Azure, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=68867f5f2f53aa49</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
+          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Engineer-Machine Learning Platform</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,24 +1046,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
+          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>AI Engineer-Machine Learning Platform</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,15 +1073,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af6f9746ce15f110</t>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7fca632ed3f48</t>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+          <t>https://www.indeed.com/viewjob?jk=af6f9746ce15f110</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Unity Catalog, Cloud Storage, Spark, Scala, MLflow, CI/CD</t>
+          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7fca632ed3f48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>RRS Enterprises</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, S3, IAM, RDS, Unity Catalog, Cloud Storage, Spark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
+          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,15 +1676,120 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>University of Utah</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
         </is>

--- a/results/job_matches_2026-04-20.xlsx
+++ b/results/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,12 +503,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Dev/ MLOps Engineer I (Full Stack)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
+          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP Data Cloud Architect with AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Agree Technologies and Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Integration Consultant</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a7d79dfeae2865</t>
+          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Integration Consultant</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c810855cd475cddf</t>
+          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Compute - New</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India Hook, SC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
+          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Business Analyst Sr</t>
+          <t>GCP Data Cloud Architect with AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
+          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Azure)</t>
+          <t>AI Integration Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68867f5f2f53aa49</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a7d79dfeae2865</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>AI Integration Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=c810855cd475cddf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Compute - New</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>India Hook, SC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Business Analyst Sr</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
+          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Site Reliability Engineer (Azure)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Azure, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=68867f5f2f53aa49</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer-Machine Learning Platform</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,112 +1081,112 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
+          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Sr. Java Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>AI Engineer-Machine Learning Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af6f9746ce15f110</t>
+          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7fca632ed3f48</t>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RRS Enterprises</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
         </is>
       </c>
     </row>
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Unity Catalog, Cloud Storage, Spark, Scala, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+          <t>https://www.indeed.com/viewjob?jk=af6f9746ce15f110</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7fca632ed3f48</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>RRS Enterprises</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, S3, IAM, RDS, Unity Catalog, Cloud Storage, Spark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,15 +1781,225 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Moon Township, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Southfield, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>University of Utah</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
         </is>

--- a/results/job_matches_2026-04-20.xlsx
+++ b/results/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Dev/ MLOps Engineer I (Full Stack)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dev/ MLOps Engineer I (Full Stack)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
+          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Data Engineer III - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agree Technologies and Solutions</t>
+          <t>Paradigm Corp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>IT Data Engineer III - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>Paradigm Corp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Lombard, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
+          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>Agree Technologies and Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GCP Data Cloud Architect with AI</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
+          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Integration Consultant</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a7d79dfeae2865</t>
+          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Integration Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c810855cd475cddf</t>
+          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
         </is>
       </c>
     </row>
@@ -958,35 +958,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Azure)</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68867f5f2f53aa49</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
+          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Sr. Java Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
+          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Java Software Engineer</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
+          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,49 +1231,49 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer-Machine Learning Platform</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af6f9746ce15f110</t>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7fca632ed3f48</t>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Experienced Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Unity Catalog, Cloud Storage, Spark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
+          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
+          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Software Engineer Go Outdoors</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+          <t>https://www.indeed.com/viewjob?jk=99e9713b85aaa6a5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Developer - Full Stack</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,112 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-20.xlsx
+++ b/results/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Compute - New</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>India Hook, SC, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
+          <t>Compute - New</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>India Hook, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
+          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Business Analyst Sr</t>
+          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
+          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Business Analyst Sr</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
+          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Java Software Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Sr. Java Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RRS Enterprises</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
         </is>
       </c>
     </row>
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RRS Enterprises</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Experienced Business Intelligence Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
+          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Experienced Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer Go Outdoors</t>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e9713b85aaa6a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Full Stack</t>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
+          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Software Engineer Go Outdoors</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
+          <t>https://www.indeed.com/viewjob?jk=99e9713b85aaa6a5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Developer - Full Stack</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2105,6 +2105,111 @@
         </is>
       </c>
       <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
         </is>
